--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.85567536279773</v>
+        <v>7.614047246454632</v>
       </c>
       <c r="D2" t="n">
-        <v>47.40443942649624</v>
+        <v>7.703221406805639</v>
       </c>
       <c r="E2" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F2" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.376518597696429</v>
+        <v>0.7111842721256698</v>
       </c>
       <c r="D3" t="n">
-        <v>4.73799505017568</v>
+        <v>0.7699241956535481</v>
       </c>
       <c r="E3" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F3" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>70.0094500724536</v>
+        <v>11.37653563677371</v>
       </c>
       <c r="D4" t="n">
-        <v>69.88923305839984</v>
+        <v>11.35700037198997</v>
       </c>
       <c r="E4" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F4" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.97340549470604</v>
+        <v>10.23317839288973</v>
       </c>
       <c r="D5" t="n">
-        <v>62.9169697270442</v>
+        <v>10.22400758064468</v>
       </c>
       <c r="E5" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F5" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.16137308052914</v>
+        <v>7.663723125585985</v>
       </c>
       <c r="D6" t="n">
-        <v>47.36859869869525</v>
+        <v>7.697397288537979</v>
       </c>
       <c r="E6" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F6" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.3666675218131</v>
+        <v>8.022083472294629</v>
       </c>
       <c r="D7" t="n">
-        <v>49.34716839702618</v>
+        <v>8.018914864516754</v>
       </c>
       <c r="E7" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F7" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.26790958388938</v>
+        <v>4.106035307382024</v>
       </c>
       <c r="D8" t="n">
-        <v>25.05204629873484</v>
+        <v>4.070957523544412</v>
       </c>
       <c r="E8" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F8" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>71.0085655609514</v>
+        <v>11.5388919036546</v>
       </c>
       <c r="D9" t="n">
-        <v>70.40650705634505</v>
+        <v>11.44105739665607</v>
       </c>
       <c r="E9" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F9" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.94713284579241</v>
+        <v>4.216409087441266</v>
       </c>
       <c r="D10" t="n">
-        <v>25.22248673079772</v>
+        <v>4.09865409375463</v>
       </c>
       <c r="E10" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F10" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.03085048352429</v>
+        <v>4.067513203572698</v>
       </c>
       <c r="D11" t="n">
-        <v>24.21734964346746</v>
+        <v>3.935319317063463</v>
       </c>
       <c r="E11" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F11" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.34372236952593</v>
+        <v>6.718354885047964</v>
       </c>
       <c r="D12" t="n">
-        <v>40.52558687747322</v>
+        <v>6.585407867589398</v>
       </c>
       <c r="E12" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F12" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>39.33831008661048</v>
+        <v>6.392475389074204</v>
       </c>
       <c r="D13" t="n">
-        <v>5.426273532033238</v>
+        <v>0.8817694489554012</v>
       </c>
       <c r="E13" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F13" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>49.73031078137178</v>
+        <v>8.081175501972915</v>
       </c>
       <c r="D14" t="n">
-        <v>10.02219758558194</v>
+        <v>1.628607107657065</v>
       </c>
       <c r="E14" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F14" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>50.46753862117332</v>
+        <v>8.200975025940664</v>
       </c>
       <c r="D15" t="n">
-        <v>49.64958241370176</v>
+        <v>8.068057142226538</v>
       </c>
       <c r="E15" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F15" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>54.57488179877803</v>
+        <v>8.868418292301429</v>
       </c>
       <c r="D16" t="n">
-        <v>51.24075945563108</v>
+        <v>8.32662341154005</v>
       </c>
       <c r="E16" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F16" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>62.67806355591873</v>
+        <v>10.18518532783679</v>
       </c>
       <c r="D17" t="n">
-        <v>53.64103942981634</v>
+        <v>8.716668907345156</v>
       </c>
       <c r="E17" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F17" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>93.61191186809594</v>
+        <v>15.21193567856559</v>
       </c>
       <c r="D18" t="n">
-        <v>64.10169871210729</v>
+        <v>10.41652604071744</v>
       </c>
       <c r="E18" t="n">
-        <v>20.49716077259347</v>
+        <v>3.330788625546439</v>
       </c>
       <c r="F18" t="n">
-        <v>21.04376657947184</v>
+        <v>3.419612069164174</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
